--- a/files/excel/IFINACC/Chart Of Account.xlsx
+++ b/files/excel/IFINACC/Chart Of Account.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danu\Documents\RPAAutomation\files\excel\IFINACC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F769AF7E-6B46-4CF1-B3D2-E4C10026BFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7FFB5A-CA10-4BCB-B5A8-B911FBF04452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -517,12 +517,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="17.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="17.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -551,7 +551,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -559,7 +559,7 @@
         <v>18</v>
       </c>
       <c r="C2" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>2</v>
@@ -568,19 +568,19 @@
         <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H2" s="2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
@@ -609,7 +609,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
